--- a/output7/【河洛文讀注音-注音二式】《道德經。第十一章》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《道德經。第十一章》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5880189-702F-4D17-81CF-3406F97A491E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD4D63C6-1A0F-4E36-B352-4FF79E5C0975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
@@ -260,18 +260,6 @@
   </si>
   <si>
     <t>經</t>
-  </si>
-  <si>
-    <t>漢字</t>
-  </si>
-  <si>
-    <t>台語音標</t>
-  </si>
-  <si>
-    <t>校正音標</t>
-  </si>
-  <si>
-    <t>座標</t>
   </si>
   <si>
     <t>(5, 5)</t>
@@ -804,6 +792,22 @@
       </rPr>
       <t>.py</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2148,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -2156,7 +2160,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -2231,7 +2235,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="30">
@@ -2255,7 +2259,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -2263,7 +2267,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30">
@@ -2315,27 +2319,27 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="60" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="60" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="60" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="60" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="60" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:2">
@@ -2356,30 +2360,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2395,44 +2399,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2451,21 +2455,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2474,26 +2478,26 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2510,32 +2514,32 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
         <v>204</v>
@@ -2544,15 +2548,15 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
@@ -2563,7 +2567,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
@@ -2572,7 +2576,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2586,7 +2590,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2600,7 +2604,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2608,13 +2612,13 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2622,13 +2626,13 @@
         <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2642,63 +2646,63 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2712,12 +2716,12 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>50</v>
@@ -2726,15 +2730,15 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -2745,16 +2749,16 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2762,27 +2766,27 @@
         <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2796,35 +2800,35 @@
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2840,30 +2844,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3005,30 +3009,30 @@
       <c r="R3" s="48"/>
       <c r="T3" s="15"/>
       <c r="V3" s="54" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="16"/>
       <c r="D4" s="58"/>
       <c r="E4" s="58" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="H4" s="58"/>
       <c r="I4" s="58" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>43</v>
       </c>
       <c r="K4" s="58" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L4" s="58" t="s">
         <v>38</v>
@@ -3047,13 +3051,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G5" s="57" t="s">
         <v>58</v>
@@ -3062,19 +3066,19 @@
         <v>19</v>
       </c>
       <c r="I5" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="57" t="s">
         <v>76</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>80</v>
       </c>
       <c r="N5" s="57" t="str">
         <f>CHAR(10)</f>
@@ -3093,26 +3097,26 @@
       <c r="C6" s="21"/>
       <c r="D6" s="59"/>
       <c r="E6" s="59" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G6" s="59" t="s">
         <v>54</v>
       </c>
       <c r="H6" s="59"/>
       <c r="I6" s="59" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L6" s="59" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -3147,22 +3151,22 @@
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="16"/>
       <c r="D8" s="58" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>205</v>
       </c>
       <c r="H8" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="58" t="s">
         <v>103</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>107</v>
       </c>
       <c r="J8" s="58"/>
       <c r="K8" s="58" t="s">
@@ -3176,16 +3180,16 @@
       </c>
       <c r="N8" s="58"/>
       <c r="O8" s="58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="Q8" s="58" t="s">
         <v>39</v>
       </c>
       <c r="R8" s="58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="S8" s="17"/>
       <c r="V8" s="55"/>
@@ -3199,25 +3203,25 @@
         <v>34</v>
       </c>
       <c r="E9" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="57" t="s">
-        <v>81</v>
-      </c>
       <c r="G9" s="57" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J9" s="57" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L9" s="57" t="s">
         <v>30</v>
@@ -3238,7 +3242,7 @@
         <v>32</v>
       </c>
       <c r="R9" s="57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="15"/>
@@ -3247,26 +3251,26 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="20"/>
       <c r="D10" s="59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="59" t="s">
         <v>102</v>
-      </c>
-      <c r="F10" s="59" t="s">
-        <v>106</v>
       </c>
       <c r="G10" s="59" t="s">
         <v>206</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J10" s="59"/>
       <c r="K10" s="59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L10" s="59" t="s">
         <v>45</v>
@@ -3276,16 +3280,16 @@
       </c>
       <c r="N10" s="59"/>
       <c r="O10" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="P10" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q10" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10" s="59" t="s">
         <v>110</v>
-      </c>
-      <c r="P10" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q10" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="R10" s="59" t="s">
-        <v>114</v>
       </c>
       <c r="S10" s="28"/>
       <c r="V10" s="55"/>
@@ -3313,7 +3317,7 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="16"/>
       <c r="D12" s="58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E12" s="58"/>
       <c r="F12" s="58"/>
@@ -3338,7 +3342,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>19</v>
@@ -3366,7 +3370,7 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="20"/>
       <c r="D14" s="59" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E14" s="59"/>
       <c r="F14" s="59"/>
@@ -3408,10 +3412,10 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="16"/>
       <c r="D16" s="58" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F16" s="58" t="s">
         <v>42</v>
@@ -3431,10 +3435,10 @@
       </c>
       <c r="L16" s="58"/>
       <c r="M16" s="58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N16" s="58" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O16" s="58" t="s">
         <v>50</v>
@@ -3443,10 +3447,10 @@
         <v>39</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="R16" s="58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="S16" s="17"/>
       <c r="V16" s="55"/>
@@ -3457,22 +3461,22 @@
         <v>4</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F17" s="57" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="57" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H17" s="57" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="57" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J17" s="57" t="s">
         <v>30</v>
@@ -3487,19 +3491,19 @@
         <v>33</v>
       </c>
       <c r="N17" s="57" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O17" s="57" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P17" s="57" t="s">
         <v>32</v>
       </c>
       <c r="Q17" s="57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R17" s="57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S17" s="19"/>
       <c r="V17" s="55"/>
@@ -3507,10 +3511,10 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="20"/>
       <c r="D18" s="59" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>42</v>
@@ -3520,7 +3524,7 @@
       </c>
       <c r="H18" s="59"/>
       <c r="I18" s="59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J18" s="59" t="s">
         <v>45</v>
@@ -3530,22 +3534,22 @@
       </c>
       <c r="L18" s="59"/>
       <c r="M18" s="59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N18" s="59" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O18" s="59" t="s">
         <v>44</v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q18" s="59" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="R18" s="59" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="S18" s="28"/>
       <c r="V18" s="55"/>
@@ -3645,7 +3649,7 @@
       <c r="D23" s="48"/>
       <c r="E23" s="48"/>
       <c r="F23" s="48" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
@@ -3664,13 +3668,13 @@
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="16"/>
       <c r="D24" s="58" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G24" s="58"/>
       <c r="H24" s="58" t="s">
@@ -3684,19 +3688,19 @@
       </c>
       <c r="K24" s="58"/>
       <c r="L24" s="58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M24" s="58" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N24" s="58" t="s">
         <v>39</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q24" s="58"/>
       <c r="R24" s="58"/>
@@ -3709,19 +3713,19 @@
         <v>6</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F25" s="57" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G25" s="57" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="57" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I25" s="57" t="s">
         <v>30</v>
@@ -3742,10 +3746,10 @@
         <v>32</v>
       </c>
       <c r="O25" s="57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P25" s="57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="57" t="s">
         <v>19</v>
@@ -3761,17 +3765,17 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="20"/>
       <c r="D26" s="59" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G26" s="59"/>
       <c r="H26" s="59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I26" s="59" t="s">
         <v>45</v>
@@ -3781,19 +3785,19 @@
       </c>
       <c r="K26" s="59"/>
       <c r="L26" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="M26" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="N26" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="O26" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="M26" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="N26" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="O26" s="59" t="s">
-        <v>114</v>
-      </c>
       <c r="P26" s="59" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="59"/>
       <c r="R26" s="59"/>
@@ -3827,10 +3831,10 @@
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="16"/>
       <c r="D28" s="58" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F28" s="58" t="s">
         <v>39</v>
@@ -3842,7 +3846,7 @@
         <v>42</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J28" s="58"/>
       <c r="K28" s="58" t="s">
@@ -3858,7 +3862,7 @@
         <v>42</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P28" s="58"/>
       <c r="Q28" s="58"/>
@@ -3876,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E29" s="57" t="s">
         <v>33</v>
@@ -3891,7 +3895,7 @@
         <v>36</v>
       </c>
       <c r="I29" s="57" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J29" s="57" t="s">
         <v>18</v>
@@ -3909,7 +3913,7 @@
         <v>36</v>
       </c>
       <c r="O29" s="57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P29" s="57" t="s">
         <v>19</v>
@@ -3930,13 +3934,13 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="20"/>
       <c r="D30" s="59" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G30" s="59" t="s">
         <v>41</v>
@@ -3945,14 +3949,14 @@
         <v>42</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J30" s="59"/>
       <c r="K30" s="59" t="s">
         <v>209</v>
       </c>
       <c r="L30" s="59" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M30" s="59" t="s">
         <v>41</v>
@@ -3961,7 +3965,7 @@
         <v>42</v>
       </c>
       <c r="O30" s="59" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P30" s="59"/>
       <c r="Q30" s="59"/>
@@ -42996,7 +43000,7 @@
       <c r="D1" s="61"/>
       <c r="E1" s="61"/>
       <c r="F1" s="71" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G1" s="71"/>
       <c r="H1" s="71"/>
@@ -43006,7 +43010,7 @@
       <c r="L1" s="65"/>
       <c r="M1" s="65"/>
       <c r="N1" s="65" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O1" s="65"/>
       <c r="P1" s="65"/>
@@ -43035,58 +43039,58 @@
     </row>
     <row r="3" spans="1:18" ht="60">
       <c r="A3" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="F3" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="G3" s="66" t="s">
         <v>151</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="67" t="s">
-        <v>153</v>
-      </c>
-      <c r="F3" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="G3" s="66" t="s">
-        <v>155</v>
       </c>
       <c r="H3" s="66" t="s">
         <v>56</v>
       </c>
       <c r="I3" s="66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J3" s="66" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K3" s="66" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L3" s="68" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M3" s="65" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="O3" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="P3" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q3" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="O3" s="65" t="s">
+      <c r="R3" s="83" t="s">
         <v>157</v>
-      </c>
-      <c r="P3" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q3" s="83" t="s">
-        <v>160</v>
-      </c>
-      <c r="R3" s="83" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5">
@@ -43094,10 +43098,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4" s="75" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D4" s="76">
         <v>20</v>
@@ -43112,37 +43116,37 @@
         <v>25000</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I4" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J4" s="79" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K4" s="79" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L4" s="70">
         <v>20000</v>
       </c>
       <c r="M4" s="70" t="s">
+        <v>160</v>
+      </c>
+      <c r="N4" s="70" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="P4" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q4" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="N4" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="O4" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="P4" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q4" s="84" t="s">
-        <v>168</v>
-      </c>
       <c r="R4" s="86" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="34.5">
@@ -43150,10 +43154,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C5" s="75" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D5" s="69">
         <v>2</v>
@@ -43168,37 +43172,37 @@
         <v>30000</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I5" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J5" s="79" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K5" s="79" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L5" s="70">
         <v>27000</v>
       </c>
       <c r="M5" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N5" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O5" s="70" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="P5" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q5" s="84" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="R5" s="86" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="34.5">
@@ -43206,10 +43210,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D6" s="69">
         <v>2</v>
@@ -43224,37 +43228,37 @@
         <v>35000</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I6" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J6" s="79" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K6" s="79" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L6" s="70">
         <v>32000</v>
       </c>
       <c r="M6" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N6" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O6" s="70" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="P6" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q6" s="84" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="R6" s="86" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5">
@@ -43262,10 +43266,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D7" s="69">
         <v>2</v>
@@ -43280,37 +43284,37 @@
         <v>40000</v>
       </c>
       <c r="H7" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I7" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J7" s="79" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K7" s="79" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L7" s="70">
         <v>37000</v>
       </c>
       <c r="M7" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N7" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O7" s="70" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P7" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q7" s="84" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="R7" s="86" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="34.5">
@@ -43318,10 +43322,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D8" s="69">
         <v>2</v>
@@ -43336,48 +43340,48 @@
         <v>45000</v>
       </c>
       <c r="H8" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I8" s="79" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J8" s="79" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K8" s="79" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L8" s="70">
         <v>42000</v>
       </c>
       <c r="M8" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N8" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O8" s="70" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="P8" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q8" s="84" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R8" s="86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="24">
       <c r="A9" s="72" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B9" s="87" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D9" s="69">
         <v>2</v>
@@ -43392,31 +43396,31 @@
         <v>47000</v>
       </c>
       <c r="H9" s="81" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I9" s="81" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J9" s="81" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K9" s="81" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L9" s="70">
         <v>44000</v>
       </c>
       <c r="M9" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N9" s="70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="O9" s="70" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="P9" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q9" s="85"/>
       <c r="R9" s="85"/>

--- a/output7/【河洛文讀注音-注音二式】《道德經。第十一章》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《道德經。第十一章》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD4D63C6-1A0F-4E36-B352-4FF79E5C0975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAF3586-6E01-4C31-AE62-17AEA73CB7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="6" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="人工標音字庫" sheetId="186" r:id="rId5"/>
     <sheet name="漢字注音" sheetId="9" r:id="rId6"/>
     <sheet name="SRT漢字注音" sheetId="189" r:id="rId7"/>
+    <sheet name="SRT漢字注音（台羅拼音）" sheetId="191" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="FILE_NAME">env!$C$5</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="216">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -260,6 +261,9 @@
   </si>
   <si>
     <t>經</t>
+  </si>
+  <si>
+    <t>漢字</t>
   </si>
   <si>
     <t>(5, 5)</t>
@@ -561,9 +565,6 @@
     <t>隱藏時刻值  （毫秒）</t>
   </si>
   <si>
-    <t>漢文</t>
-  </si>
-  <si>
     <t>漢字標音</t>
   </si>
   <si>
@@ -603,9 +604,6 @@
     <t>27</t>
   </si>
   <si>
-    <t>卅輻同一轂，當其無，有車之用也。</t>
-  </si>
-  <si>
     <t>Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</t>
   </si>
   <si>
@@ -640,9 +638,6 @@
   </si>
   <si>
     <t>鑿戶牖，當其無，有室之用也。</t>
-  </si>
-  <si>
-    <t>Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</t>
   </si>
   <si>
     <t>00:00:40,000</t>
@@ -856,6 +851,32 @@
     <t>bbu5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三十輻同一轂，當其無，有車之用也。</t>
+  </si>
+  <si>
+    <t>Tsha̍k hōo iú, tong kî bô, íu sik tsi īong ía.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dor7 diek4 ging1. De7 ship8 it4 jiong1</t>
+  </si>
+  <si>
+    <t>Sam1 ship8 hok4 dong5 it4 gok4, dong1 gi5 bbu5, iu2 gu1 ji1 iong7 ia2.</t>
+  </si>
+  <si>
+    <t>Ian5 shit8 ui5 ki3, dong1 gi5 bbu5, iu2 shit8 ki3 ji1 iong7 ia2.</t>
+  </si>
+  <si>
+    <t>Cak8 hoo7 iu2, dong1 gi5 bbu5, iu2 shiek4 ji1 iong7 ia2.</t>
+  </si>
+  <si>
+    <t>Goo3 iu2 ji1 i2 ui5 li7, bbu5 ji1 i2 ui5 iong7.</t>
+  </si>
 </sst>
 </file>
 
@@ -866,7 +887,7 @@
     <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="181" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="56">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1213,14 +1234,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFF00"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1607,8 +1620,17 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1672,23 +1694,14 @@
     <xf numFmtId="0" fontId="47" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="47" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -2152,7 +2165,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -2160,7 +2173,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -2235,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="30">
@@ -2259,7 +2272,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -2267,7 +2280,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30">
@@ -2319,32 +2332,32 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="60" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="60" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="60" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="60" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="60" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="60" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2360,30 +2373,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" t="s">
         <v>199</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>200</v>
-      </c>
-      <c r="C1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2399,44 +2412,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" t="s">
         <v>199</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>200</v>
-      </c>
-      <c r="C1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2455,21 +2468,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2478,26 +2491,26 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2514,49 +2527,49 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
@@ -2567,7 +2580,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
@@ -2576,7 +2589,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2590,7 +2603,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2598,13 +2611,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2612,13 +2625,13 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2626,13 +2639,13 @@
         <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2646,63 +2659,63 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2716,12 +2729,12 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>50</v>
@@ -2730,15 +2743,15 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -2749,16 +2762,16 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2766,27 +2779,27 @@
         <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2800,35 +2813,35 @@
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2844,30 +2857,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" t="s">
         <v>199</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>200</v>
-      </c>
-      <c r="C1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3009,30 +3022,30 @@
       <c r="R3" s="48"/>
       <c r="T3" s="15"/>
       <c r="V3" s="54" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="16"/>
       <c r="D4" s="58"/>
       <c r="E4" s="58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>49</v>
       </c>
       <c r="H4" s="58"/>
       <c r="I4" s="58" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" s="58" t="s">
         <v>43</v>
       </c>
       <c r="K4" s="58" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L4" s="58" t="s">
         <v>38</v>
@@ -3051,13 +3064,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G5" s="57" t="s">
         <v>58</v>
@@ -3066,19 +3079,19 @@
         <v>19</v>
       </c>
       <c r="I5" s="57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J5" s="57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K5" s="57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L5" s="57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M5" s="57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N5" s="57" t="str">
         <f>CHAR(10)</f>
@@ -3097,26 +3110,26 @@
       <c r="C6" s="21"/>
       <c r="D6" s="59"/>
       <c r="E6" s="59" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" s="59" t="s">
         <v>54</v>
       </c>
       <c r="H6" s="59"/>
       <c r="I6" s="59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K6" s="59" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L6" s="59" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -3151,22 +3164,22 @@
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="16"/>
       <c r="D8" s="58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I8" s="58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" s="58"/>
       <c r="K8" s="58" t="s">
@@ -3176,20 +3189,20 @@
         <v>52</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N8" s="58"/>
       <c r="O8" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q8" s="58" t="s">
         <v>39</v>
       </c>
       <c r="R8" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S8" s="17"/>
       <c r="V8" s="55"/>
@@ -3203,25 +3216,25 @@
         <v>34</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" s="57" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L9" s="57" t="s">
         <v>30</v>
@@ -3242,7 +3255,7 @@
         <v>32</v>
       </c>
       <c r="R9" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="15"/>
@@ -3251,45 +3264,45 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="20"/>
       <c r="D10" s="59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J10" s="59"/>
       <c r="K10" s="59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L10" s="59" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N10" s="59"/>
       <c r="O10" s="59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P10" s="59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q10" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R10" s="59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S10" s="28"/>
       <c r="V10" s="55"/>
@@ -3317,7 +3330,7 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="16"/>
       <c r="D12" s="58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" s="58"/>
       <c r="F12" s="58"/>
@@ -3342,7 +3355,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>19</v>
@@ -3370,7 +3383,7 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="20"/>
       <c r="D14" s="59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14" s="59"/>
       <c r="F14" s="59"/>
@@ -3412,10 +3425,10 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="16"/>
       <c r="D16" s="58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F16" s="58" t="s">
         <v>42</v>
@@ -3431,14 +3444,14 @@
         <v>52</v>
       </c>
       <c r="K16" s="58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L16" s="58"/>
       <c r="M16" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N16" s="58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O16" s="58" t="s">
         <v>50</v>
@@ -3447,10 +3460,10 @@
         <v>39</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R16" s="58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S16" s="17"/>
       <c r="V16" s="55"/>
@@ -3461,22 +3474,22 @@
         <v>4</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" s="57" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" s="57" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J17" s="57" t="s">
         <v>30</v>
@@ -3491,19 +3504,19 @@
         <v>33</v>
       </c>
       <c r="N17" s="57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O17" s="57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P17" s="57" t="s">
         <v>32</v>
       </c>
       <c r="Q17" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R17" s="57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S17" s="19"/>
       <c r="V17" s="55"/>
@@ -3511,10 +3524,10 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="20"/>
       <c r="D18" s="59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>42</v>
@@ -3524,32 +3537,32 @@
       </c>
       <c r="H18" s="59"/>
       <c r="I18" s="59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J18" s="59" t="s">
         <v>45</v>
       </c>
       <c r="K18" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L18" s="59"/>
       <c r="M18" s="59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N18" s="59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O18" s="59" t="s">
         <v>44</v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q18" s="59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R18" s="59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S18" s="28"/>
       <c r="V18" s="55"/>
@@ -3649,7 +3662,7 @@
       <c r="D23" s="48"/>
       <c r="E23" s="48"/>
       <c r="F23" s="48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
@@ -3668,13 +3681,13 @@
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="16"/>
       <c r="D24" s="58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G24" s="58"/>
       <c r="H24" s="58" t="s">
@@ -3684,23 +3697,23 @@
         <v>52</v>
       </c>
       <c r="J24" s="58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K24" s="58"/>
       <c r="L24" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M24" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N24" s="58" t="s">
         <v>39</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q24" s="58"/>
       <c r="R24" s="58"/>
@@ -3713,19 +3726,19 @@
         <v>6</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F25" s="57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" s="57" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I25" s="57" t="s">
         <v>30</v>
@@ -3746,10 +3759,10 @@
         <v>32</v>
       </c>
       <c r="O25" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P25" s="57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="57" t="s">
         <v>19</v>
@@ -3765,39 +3778,39 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="20"/>
       <c r="D26" s="59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G26" s="59"/>
       <c r="H26" s="59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" s="59" t="s">
         <v>45</v>
       </c>
       <c r="J26" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K26" s="59"/>
       <c r="L26" s="59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M26" s="59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N26" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O26" s="59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q26" s="59"/>
       <c r="R26" s="59"/>
@@ -3831,10 +3844,10 @@
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="16"/>
       <c r="D28" s="58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="58" t="s">
         <v>39</v>
@@ -3846,11 +3859,11 @@
         <v>42</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J28" s="58"/>
       <c r="K28" s="58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L28" s="58" t="s">
         <v>39</v>
@@ -3862,7 +3875,7 @@
         <v>42</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="58"/>
       <c r="Q28" s="58"/>
@@ -3880,7 +3893,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E29" s="57" t="s">
         <v>33</v>
@@ -3895,7 +3908,7 @@
         <v>36</v>
       </c>
       <c r="I29" s="57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J29" s="57" t="s">
         <v>18</v>
@@ -3913,10 +3926,10 @@
         <v>36</v>
       </c>
       <c r="O29" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P29" s="57" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="Q29" s="57" t="str">
         <f>CHAR(10)</f>
@@ -3934,13 +3947,13 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="20"/>
       <c r="D30" s="59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G30" s="59" t="s">
         <v>41</v>
@@ -3949,14 +3962,14 @@
         <v>42</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J30" s="59"/>
       <c r="K30" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L30" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M30" s="59" t="s">
         <v>41</v>
@@ -3965,7 +3978,7 @@
         <v>42</v>
       </c>
       <c r="O30" s="59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P30" s="59"/>
       <c r="Q30" s="59"/>
@@ -42993,437 +43006,864 @@
     <col min="18" max="18" width="82.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24">
-      <c r="A1" s="61"/>
-      <c r="B1" s="64"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="71" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="64"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
     </row>
     <row r="3" spans="1:18" ht="60">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="69" t="s">
+        <v>154</v>
+      </c>
+      <c r="K3" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="L3" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="O3" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="85" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="34.5">
+      <c r="A4" s="66">
+        <v>1</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="79">
+        <v>20</v>
+      </c>
+      <c r="E4" s="79">
+        <v>25</v>
+      </c>
+      <c r="F4" s="80">
+        <v>0</v>
+      </c>
+      <c r="G4" s="81">
+        <v>25000</v>
+      </c>
+      <c r="H4" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J4" s="82" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="73">
+        <v>20000</v>
+      </c>
+      <c r="M4" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N4" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="P4" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q4" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="R4" s="62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="69">
+      <c r="A5" s="66">
+        <v>2</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="72">
+        <v>2</v>
+      </c>
+      <c r="E5" s="72">
+        <v>5</v>
+      </c>
+      <c r="F5" s="80">
+        <v>25000</v>
+      </c>
+      <c r="G5" s="81">
+        <v>30000</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L5" s="73">
+        <v>27000</v>
+      </c>
+      <c r="M5" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N5" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O5" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="P5" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q5" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="R5" s="62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="69">
+      <c r="A6" s="66">
+        <v>3</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="78" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="72">
+        <v>2</v>
+      </c>
+      <c r="E6" s="72">
+        <v>5</v>
+      </c>
+      <c r="F6" s="80">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="81">
+        <v>35000</v>
+      </c>
+      <c r="H6" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="K6" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L6" s="73">
+        <v>32000</v>
+      </c>
+      <c r="M6" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N6" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O6" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="P6" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q6" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="R6" s="62" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="34.5">
+      <c r="A7" s="66">
+        <v>4</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="72">
+        <v>2</v>
+      </c>
+      <c r="E7" s="72">
+        <v>5</v>
+      </c>
+      <c r="F7" s="80">
+        <v>35000</v>
+      </c>
+      <c r="G7" s="81">
+        <v>40000</v>
+      </c>
+      <c r="H7" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="82" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L7" s="73">
+        <v>37000</v>
+      </c>
+      <c r="M7" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N7" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O7" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="P7" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q7" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="R7" s="62" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="34.5">
+      <c r="A8" s="66">
+        <v>5</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="72">
+        <v>2</v>
+      </c>
+      <c r="E8" s="72">
+        <v>5</v>
+      </c>
+      <c r="F8" s="80">
+        <v>40000</v>
+      </c>
+      <c r="G8" s="81">
+        <v>45000</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J8" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L8" s="73">
+        <v>42000</v>
+      </c>
+      <c r="M8" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N8" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O8" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="P8" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q8" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="R8" s="62" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="24">
+      <c r="A9" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="72">
+        <v>2</v>
+      </c>
+      <c r="E9" s="72">
+        <v>5</v>
+      </c>
+      <c r="F9" s="83">
+        <v>42000</v>
+      </c>
+      <c r="G9" s="81">
+        <v>47000</v>
+      </c>
+      <c r="H9" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="J9" s="84" t="s">
+        <v>190</v>
+      </c>
+      <c r="K9" s="84" t="s">
+        <v>162</v>
+      </c>
+      <c r="L9" s="73">
+        <v>44000</v>
+      </c>
+      <c r="M9" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N9" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O9" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="P9" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622B9C83-244B-450E-989F-5E05F3CCE6DE}">
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="9" style="64"/>
+    <col min="2" max="3" width="14.125" style="64" customWidth="1"/>
+    <col min="4" max="5" width="9" style="64"/>
+    <col min="6" max="11" width="0" style="64" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="16" width="12" style="64" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="68.875" style="64" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="82.75" style="64" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="64"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="B1" s="67"/>
+      <c r="F1" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+    </row>
+    <row r="3" spans="1:18" ht="60">
+      <c r="A3" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="B3" s="65" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="C3" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="D3" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="E3" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="F3" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="G3" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="J3" s="66" t="s">
+      <c r="I3" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="J3" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="L3" s="68" t="s">
+      <c r="K3" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="M3" s="65" t="s">
+      <c r="L3" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="O3" s="65" t="s">
+      <c r="N3" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="P3" s="65" t="s">
+      <c r="O3" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="Q3" s="83" t="s">
-        <v>156</v>
-      </c>
-      <c r="R3" s="83" t="s">
+      <c r="P3" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="85" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5">
-      <c r="A4" s="63">
+      <c r="A4" s="66">
         <v>1</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="79">
         <v>20</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="79">
         <v>25</v>
       </c>
-      <c r="F4" s="77">
+      <c r="F4" s="80">
         <v>0</v>
       </c>
-      <c r="G4" s="78">
+      <c r="G4" s="81">
         <v>25000</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="K4" s="79" t="s">
+      <c r="K4" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="L4" s="70">
+      <c r="L4" s="73">
         <v>20000</v>
       </c>
-      <c r="M4" s="70" t="s">
+      <c r="M4" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="N4" s="70" t="s">
+      <c r="N4" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="O4" s="70" t="s">
+      <c r="O4" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="P4" s="70" t="s">
+      <c r="P4" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="Q4" s="84" t="s">
+      <c r="Q4" s="63" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="86" t="s">
+      <c r="R4" s="87" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="34.5">
-      <c r="A5" s="63">
+      <c r="A5" s="66">
         <v>2</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="78" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="72">
         <v>2</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="72">
         <v>5</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="80">
         <v>25000</v>
       </c>
-      <c r="G5" s="78">
+      <c r="G5" s="81">
         <v>30000</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="H5" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="I5" s="79" t="s">
+      <c r="I5" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="J5" s="79" t="s">
+      <c r="J5" s="82" t="s">
         <v>168</v>
       </c>
-      <c r="K5" s="79" t="s">
+      <c r="K5" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="73">
         <v>27000</v>
       </c>
-      <c r="M5" s="70" t="s">
+      <c r="M5" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="N5" s="70" t="s">
+      <c r="N5" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="O5" s="70" t="s">
+      <c r="O5" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="P5" s="70" t="s">
+      <c r="P5" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="Q5" s="84" t="s">
+      <c r="Q5" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="R5" s="87" t="s">
         <v>170</v>
       </c>
-      <c r="R5" s="86" t="s">
+    </row>
+    <row r="6" spans="1:18" ht="34.5">
+      <c r="A6" s="66">
+        <v>3</v>
+      </c>
+      <c r="B6" s="77" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="34.5">
-      <c r="A6" s="63">
-        <v>3</v>
-      </c>
-      <c r="B6" s="74" t="s">
+      <c r="C6" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="D6" s="72">
+        <v>2</v>
+      </c>
+      <c r="E6" s="72">
+        <v>5</v>
+      </c>
+      <c r="F6" s="80">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="81">
+        <v>35000</v>
+      </c>
+      <c r="H6" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="69">
+      <c r="K6" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="L6" s="73">
+        <v>32000</v>
+      </c>
+      <c r="M6" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="N6" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="O6" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="P6" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q6" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="R6" s="87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="34.5">
+      <c r="A7" s="66">
+        <v>4</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="72">
         <v>2</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E7" s="72">
         <v>5</v>
       </c>
-      <c r="F6" s="77">
-        <v>30000</v>
-      </c>
-      <c r="G6" s="78">
+      <c r="F7" s="80">
         <v>35000</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="G7" s="81">
+        <v>40000</v>
+      </c>
+      <c r="H7" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I7" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="79" t="s">
-        <v>174</v>
-      </c>
-      <c r="K6" s="79" t="s">
+      <c r="J7" s="82" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="L6" s="70">
-        <v>32000</v>
-      </c>
-      <c r="M6" s="70" t="s">
+      <c r="L7" s="73">
+        <v>37000</v>
+      </c>
+      <c r="M7" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N7" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="O6" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="P6" s="70" t="s">
+      <c r="O7" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="P7" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="Q6" s="84" t="s">
-        <v>176</v>
-      </c>
-      <c r="R6" s="86" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="34.5">
-      <c r="A7" s="63">
-        <v>4</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="69">
+      <c r="Q7" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="R7" s="87" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="34.5">
+      <c r="A8" s="66">
+        <v>5</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="72">
         <v>2</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E8" s="72">
         <v>5</v>
       </c>
-      <c r="F7" s="77">
-        <v>35000</v>
-      </c>
-      <c r="G7" s="78">
+      <c r="F8" s="80">
         <v>40000</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="G8" s="81">
+        <v>45000</v>
+      </c>
+      <c r="H8" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="I7" s="79" t="s">
+      <c r="I8" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="J7" s="79" t="s">
-        <v>180</v>
-      </c>
-      <c r="K7" s="79" t="s">
+      <c r="J8" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="L7" s="70">
-        <v>37000</v>
-      </c>
-      <c r="M7" s="70" t="s">
+      <c r="L8" s="73">
+        <v>42000</v>
+      </c>
+      <c r="M8" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="N7" s="70" t="s">
+      <c r="N8" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="O7" s="70" t="s">
-        <v>181</v>
-      </c>
-      <c r="P7" s="70" t="s">
+      <c r="O8" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="P8" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="Q7" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="R7" s="86" t="s">
+      <c r="Q8" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="R8" s="87" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="24">
+      <c r="A9" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="86" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="34.5">
-      <c r="A8" s="63">
+      <c r="C9" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="72">
+        <v>2</v>
+      </c>
+      <c r="E9" s="72">
         <v>5</v>
       </c>
-      <c r="B8" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="69">
-        <v>2</v>
-      </c>
-      <c r="E8" s="69">
-        <v>5</v>
-      </c>
-      <c r="F8" s="77">
-        <v>40000</v>
-      </c>
-      <c r="G8" s="78">
-        <v>45000</v>
-      </c>
-      <c r="H8" s="79" t="s">
+      <c r="F9" s="83">
+        <v>42000</v>
+      </c>
+      <c r="G9" s="81">
+        <v>47000</v>
+      </c>
+      <c r="H9" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I9" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="J8" s="79" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="79" t="s">
+      <c r="J9" s="84" t="s">
+        <v>190</v>
+      </c>
+      <c r="K9" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="L8" s="70">
-        <v>42000</v>
-      </c>
-      <c r="M8" s="70" t="s">
+      <c r="L9" s="73">
+        <v>44000</v>
+      </c>
+      <c r="M9" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="N8" s="70" t="s">
+      <c r="N9" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="O8" s="70" t="s">
-        <v>187</v>
-      </c>
-      <c r="P8" s="70" t="s">
+      <c r="O9" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="P9" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="Q8" s="84" t="s">
-        <v>188</v>
-      </c>
-      <c r="R8" s="86" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="24">
-      <c r="A9" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="87" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="D9" s="69">
-        <v>2</v>
-      </c>
-      <c r="E9" s="69">
-        <v>5</v>
-      </c>
-      <c r="F9" s="80">
-        <v>42000</v>
-      </c>
-      <c r="G9" s="78">
-        <v>47000</v>
-      </c>
-      <c r="H9" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="I9" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="J9" s="81" t="s">
-        <v>192</v>
-      </c>
-      <c r="K9" s="81" t="s">
-        <v>162</v>
-      </c>
-      <c r="L9" s="70">
-        <v>44000</v>
-      </c>
-      <c r="M9" s="70" t="s">
-        <v>160</v>
-      </c>
-      <c r="N9" s="70" t="s">
-        <v>160</v>
-      </c>
-      <c r="O9" s="70" t="s">
-        <v>193</v>
-      </c>
-      <c r="P9" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q9" s="85"/>
-      <c r="R9" s="85"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
